--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66488096</v>
+        <v>87047777</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Valhall, Hjd</t>
+          <t>Myttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411659.9515223913</v>
+        <v>412021</v>
       </c>
       <c r="R2" t="n">
-        <v>6971508.735250427</v>
+        <v>6971474</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-06-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,79 +757,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>5480</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87047777</v>
+        <v>66488096</v>
       </c>
       <c r="B3" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Myttjärnen, Hjd</t>
+          <t>Valhall, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412020.7877574418</v>
+        <v>411660</v>
       </c>
       <c r="R3" t="n">
-        <v>6971473.902722311</v>
+        <v>6971509</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,22 +859,132 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>5480</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>87047730</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Myttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>412024</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6971381</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-07-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-07-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spetten.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,6 +990,1445 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135121197</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411723</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971330</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135121198</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>411723</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6971336</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135121199</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>411745</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6971357</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135121200</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>411716</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6971392</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135121206</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>411761</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6971555</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135121207</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>411812</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971502</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135121208</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411810</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971498</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135121209</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>411833</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6971448</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135121210</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>411852</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6971456</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135121211</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>411856</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6971466</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135121212</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>411872</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6971463</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135121213</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>411910</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6971497</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135121214</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>411910</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6971488</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135121215</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>411791</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6971313</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2429,6 +2429,435 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135463354</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 25616-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>411482</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6971588</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135463012</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135463024</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135463101</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 25616-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>411687</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6971545</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87047777</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66488096</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87047730</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121197</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121198</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121199</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,6 +1432,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121200</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1499,6 +1539,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121206</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121207</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1703,6 +1753,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121208</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1805,6 +1860,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121209</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1907,6 +1967,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121210</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2009,6 +2074,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121211</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2111,6 +2181,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121212</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2213,6 +2288,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121213</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2315,6 +2395,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121214</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2428,6 +2513,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121215</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2538,6 +2628,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463354</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2647,6 +2742,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463012</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2752,6 +2852,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463024</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2857,8 +2962,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463101</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>135121197</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>135121198</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>135121199</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135121200</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>135121206</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135121207</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>135121208</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>135121209</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>135121210</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>135121211</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135121212</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>135121213</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>135121214</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>135121215</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>135463354</v>
       </c>
       <c r="B19" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>135463012</v>
       </c>
       <c r="B20" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>135463024</v>
       </c>
       <c r="B21" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>135463101</v>
       </c>
       <c r="B22" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2516,6 +2516,455 @@
       <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135121215</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135463354</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 25616-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>411482</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6971588</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463354</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135463012</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463012</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135463024</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135463101</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 25616-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>411687</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6971545</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463101</t>
         </is>
       </c>
     </row>
@@ -2538,6 +2987,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,61 +1012,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135121215</v>
+        <v>135121197</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411791</v>
+        <v>411723</v>
       </c>
       <c r="R5" t="n">
-        <v>6971313</v>
+        <v>6971330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,6 +1085,11 @@
           <t>2026-07-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1124,59 +1113,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121215</t>
+          <t>https://artportalen.se/Sighting/135121197</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135463354</v>
+        <v>135121198</v>
       </c>
       <c r="B6" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 25616-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411482</v>
+        <v>411723</v>
       </c>
       <c r="R6" t="n">
-        <v>6971588</v>
+        <v>6971336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,17 +1184,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,27 +1209,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463354</t>
+          <t>https://artportalen.se/Sighting/135121198</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135463012</v>
+        <v>135121199</v>
       </c>
       <c r="B7" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,46 +1237,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 25683-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411892</v>
+        <v>411745</v>
       </c>
       <c r="R7" t="n">
-        <v>6971406</v>
+        <v>6971357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,12 +1291,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,44 +1316,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463012</t>
+          <t>https://artportalen.se/Sighting/135121199</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135463024</v>
+        <v>135121200</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1387,25 +1361,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 25683-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411892</v>
+        <v>411716</v>
       </c>
       <c r="R8" t="n">
-        <v>6971406</v>
+        <v>6971392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,12 +1398,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,27 +1423,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463024</t>
+          <t>https://artportalen.se/Sighting/135121200</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135463101</v>
+        <v>135121206</v>
       </c>
       <c r="B9" t="n">
-        <v>58084</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,16 +1451,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1497,25 +1468,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 25616-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411687</v>
+        <v>411761</v>
       </c>
       <c r="R9" t="n">
-        <v>6971545</v>
+        <v>6971555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,12 +1505,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,16 +1530,1439 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121206</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135121207</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>411812</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971502</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121207</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135121208</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411810</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971498</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121208</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135121209</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>411833</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6971448</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121209</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135121210</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>411852</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6971456</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121210</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135121211</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>411856</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6971466</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121211</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135121212</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>411872</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6971463</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121212</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135121213</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>411910</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6971497</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121213</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135121214</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>411910</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6971488</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121214</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135121215</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>411791</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6971313</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121215</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135463354</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 25616-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>411482</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6971588</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463354</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135463012</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463012</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135463024</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135463101</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 25616-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>411687</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6971545</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463101</t>
         </is>
@@ -1587,6 +2978,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>135121197</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>135121198</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>135121199</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135121200</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>135121206</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135121207</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>135121208</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>135121209</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>135121210</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>135121211</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135121212</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>135121213</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>135121214</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>135463354</v>
       </c>
       <c r="B19" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>135463012</v>
       </c>
       <c r="B20" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>135463024</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>135463101</v>
       </c>
       <c r="B22" t="n">
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,61 +1012,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135121215</v>
+        <v>135121197</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>57982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411791</v>
+        <v>411723</v>
       </c>
       <c r="R5" t="n">
-        <v>6971313</v>
+        <v>6971330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,6 +1085,11 @@
           <t>2026-07-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1124,59 +1113,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121215</t>
+          <t>https://artportalen.se/Sighting/135121197</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135463354</v>
+        <v>135121198</v>
       </c>
       <c r="B6" t="n">
-        <v>57169</v>
+        <v>57982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 25616-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411482</v>
+        <v>411723</v>
       </c>
       <c r="R6" t="n">
-        <v>6971588</v>
+        <v>6971336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,17 +1184,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,27 +1209,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463354</t>
+          <t>https://artportalen.se/Sighting/135121198</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135463012</v>
+        <v>135121199</v>
       </c>
       <c r="B7" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,46 +1237,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 25683-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411892</v>
+        <v>411745</v>
       </c>
       <c r="R7" t="n">
-        <v>6971406</v>
+        <v>6971357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,12 +1291,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,44 +1316,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463012</t>
+          <t>https://artportalen.se/Sighting/135121199</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135463024</v>
+        <v>135121200</v>
       </c>
       <c r="B8" t="n">
-        <v>58138</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1387,25 +1361,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 25683-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411892</v>
+        <v>411716</v>
       </c>
       <c r="R8" t="n">
-        <v>6971406</v>
+        <v>6971392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,12 +1398,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,27 +1423,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463024</t>
+          <t>https://artportalen.se/Sighting/135121200</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135463101</v>
+        <v>135121206</v>
       </c>
       <c r="B9" t="n">
-        <v>58086</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,16 +1451,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1497,25 +1468,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 25616-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411687</v>
+        <v>411761</v>
       </c>
       <c r="R9" t="n">
-        <v>6971545</v>
+        <v>6971555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,12 +1505,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,16 +1530,1439 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121206</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135121207</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>411812</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971502</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121207</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135121208</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411810</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971498</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121208</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135121209</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>411833</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6971448</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121209</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135121210</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>411852</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6971456</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121210</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135121211</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>411856</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6971466</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121211</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135121212</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>411872</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6971463</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121212</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135121213</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>411910</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6971497</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121213</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135121214</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>411910</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6971488</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121214</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135121215</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>411791</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6971313</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121215</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135463354</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 25616-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>411482</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6971588</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463354</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135463012</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463012</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135463024</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135463101</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58086</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 25616-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>411687</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6971545</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463101</t>
         </is>
@@ -1587,6 +2978,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>135121197</v>
       </c>
       <c r="B5" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>135121198</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>135121199</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135121200</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>135121206</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135121207</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>135121208</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>135121209</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>135121210</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>135121211</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135121212</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>135121213</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>135121214</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>135121197</v>
       </c>
       <c r="B5" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>135121198</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>135121199</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135121200</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>135121206</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135121207</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>135121208</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>135121209</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>135121210</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>135121211</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135121212</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>135121213</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>135121214</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>135121197</v>
       </c>
       <c r="B5" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>135121198</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>135121199</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135121200</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>135121206</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135121207</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>135121208</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>135121209</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>135121210</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>135121211</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135121212</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>135121213</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>135121214</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -1015,7 +1015,7 @@
         <v>135121197</v>
       </c>
       <c r="B5" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>135121198</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>135121199</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135121200</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>135121206</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135121207</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>135121208</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>135121209</v>
       </c>
       <c r="B12" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>135121210</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>135121211</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135121212</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>135121213</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>135121214</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25616-2026 artfynd.xlsx
+++ b/artfynd/A 25616-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,61 +1012,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135121215</v>
+        <v>135121197</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>58006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411791</v>
+        <v>411723</v>
       </c>
       <c r="R5" t="n">
-        <v>6971313</v>
+        <v>6971330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,6 +1085,11 @@
           <t>2026-07-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1124,59 +1113,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121215</t>
+          <t>https://artportalen.se/Sighting/135121197</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135463354</v>
+        <v>135121198</v>
       </c>
       <c r="B6" t="n">
-        <v>57169</v>
+        <v>58006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 25616-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411482</v>
+        <v>411723</v>
       </c>
       <c r="R6" t="n">
-        <v>6971588</v>
+        <v>6971336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,17 +1184,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,27 +1209,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463354</t>
+          <t>https://artportalen.se/Sighting/135121198</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135463012</v>
+        <v>135121199</v>
       </c>
       <c r="B7" t="n">
-        <v>58143</v>
+        <v>58006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,46 +1237,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 25683-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411892</v>
+        <v>411745</v>
       </c>
       <c r="R7" t="n">
-        <v>6971406</v>
+        <v>6971357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,12 +1291,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,44 +1316,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463012</t>
+          <t>https://artportalen.se/Sighting/135121199</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135463024</v>
+        <v>135121200</v>
       </c>
       <c r="B8" t="n">
-        <v>58138</v>
+        <v>58006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1387,25 +1361,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 25683-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411892</v>
+        <v>411716</v>
       </c>
       <c r="R8" t="n">
-        <v>6971406</v>
+        <v>6971392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,12 +1398,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,27 +1423,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463024</t>
+          <t>https://artportalen.se/Sighting/135121200</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135463101</v>
+        <v>135121206</v>
       </c>
       <c r="B9" t="n">
-        <v>58086</v>
+        <v>58006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,16 +1451,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1497,25 +1468,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 25616-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411687</v>
+        <v>411761</v>
       </c>
       <c r="R9" t="n">
-        <v>6971545</v>
+        <v>6971555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,12 +1505,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,16 +1530,1439 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121206</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135121207</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>411812</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971502</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121207</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135121208</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411810</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971498</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121208</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135121209</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>411833</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6971448</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121209</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135121210</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>411852</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6971456</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121210</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135121211</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>411856</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6971466</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121211</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135121212</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>411872</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6971463</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121212</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135121213</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>411910</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6971497</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121213</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135121214</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>411910</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6971488</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121214</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135121215</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>411791</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6971313</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121215</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135463354</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 25616-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>411482</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6971588</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463354</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135463012</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463012</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135463024</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135463101</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58086</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 25616-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>411687</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6971545</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463101</t>
         </is>
@@ -1587,6 +2978,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
